--- a/260718.xlsx
+++ b/260718.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9E3EBD-23B5-4957-B8DE-9D4D30D6A313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711F4FD2-F41C-47AB-AB4F-2A4FDD550C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9260" yWindow="4110" windowWidth="16150" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9260" yWindow="4110" windowWidth="16150" windowHeight="11170" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -29,234 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>每周采访-160731-Generalbundesanwalt</t>
-  </si>
-  <si>
-    <t>每周采访-160807-Bundesweh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每周采访-160814-sigmar</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每周采访-160828-Frod</t>
-  </si>
-  <si>
-    <t>um hier dann eben Mobilitätsdienstleistungen anbieten zu können.
-"""""""""""""""""""""""""""""""" Mit der Politik an Rahmenbedingungen für autonomes Fahren arbeiten"""""""""""""""""""""""""""""""" Hahne: Er muss das Fahrzeug aber überwachen.
-Mattes: Das kommt auf die Rahmenbedingungen an, die gesetzt werden.
-Heute haben wir gesetzliche Rahmenbedingungen, die den Fahrer grundsätzlich noch vollständig verantwortlich machen.
-Deswegen müssen wir mit der Politik auch an den Rahmenbedingungen für autonomes Fahren arbeiten.
-Aber dieses Fahrzeug, diese Stufe von autonom fahrenden Fahrzeug, kann sich eigenständig bewegen und auch die Insassen bewegen und es ist nicht notwendig, dass Fahrerinnen oder Fahrer tatsächlich eingreifen.
-Weil wir glauben und sicher sind, dass eben viele Mobilitätsdienstleistungen und Nachfragen genau in diese Richtung gehen, dass man individuell mobil sein will, sehr flexibel von Ort zu Ort kommen will, aber nicht unbedingt dieses Fahrzeug mehr besitzen.
-Und in der Zeit, wo man unterwegs ist, vielleicht etwas anderes noch Sinnvolleres tun kann, als zum Beispiel urban, in einer großen Stadt, dem Verkehr seine Aufmerksamkeit zu schenken, sondern eben gerade etwas anderes zu tun.
-Hahne: Wenn Sie von der Stadt sprechen, in Zukunft soll ja das gesamte Verkehrssystem mal autonom sein, so der Traum.
-Da braucht man ja einheitliche Standards, damit die Systeme auch kommunizieren können, damit es nicht zu Unfällen kommt.
-Wie kann das gelingen, wenn jeder Hersteller erstmal sein eigenes Süppchen kocht?
-Wie arbeiten Sie da zusammen?
-Mattes: Die Entwicklung von Rahmenbedingungen für autonom fahrende Fahrzeuge, das ist natürlich eine Sache, die über die Hersteller, mit der Politik und den rahmensetzenden Gremien, hinausgeht.
-Hier sind die Verbände gefordert – auf der einen Seite der VDA, ACEA oder aber auch andere Verbände in den USA. Es ist auch ein klassisches Feld, wo eben es noch keine neuen Rahmenbedingungen gibt, wo wir sehr, sehr gut in transatlantischen Verhältnissen Rahmenbedingungen entwickeln könnten, die dann sowohl in den USA als auch in Europa gelten können.
-Und wir müssten dann bei den Produkten eben auch keine unterschiedlichen Umsetzungen machen.
-Und das würde natürlich das Ganze auch erleichtern.
-Hahne: Ich höre hier allerdings auch viel den Konjunktiv.
-Das heißt, noch ist die Politik da nicht Ihren Wünschen gemäß dem nachgekommen?
-Mattes: Nein, wir sind eben noch nicht an einem Punkt, wo wir sagen können, da liegt was vor, über das wir uns jetzt austauschen können.
-Aber natürlich ist die Politik involviert und kümmert sich auch da drum gemeinsam mit uns.
-Es gibt ja auch die Testfelder schon, es gibt die Regionen, wo autonom erprobt werden darf.
-Und wir müssen jetzt aus diesen ganzen Erprobungen heraus dann auch die richtigen Rahmenbedingungen setzen, das ist klar.
-Hahne: Sie haben es angesprochen, 2021 will Ford Fahrdiensten wie Uber zum Beispiel selbstfahrende Autos anbieten.
-Wann, glauben Sie, werden denn Otto–Normal-Kunden das erste selbstfahrende Ford-Auto kaufen können?
-Mattes: 2021.
-Denn dann werden wir diese Fahrzeuge tatsächlich auf den Markt bringen.
-Ich bin aber überzeugt, dass die größte Nachfrage nicht bei denjenigen sein wird, die die Fahrzeuge direkt kaufen, sondern vielmehr, die solche Fahrzeuge nutzen, die halt von A nach B in die Welt gebracht werden wollen, aber nicht unbedingt sagen, das Auto muss mir gehören.
-Hahne: Zu Gast im Deutschlandfunk Interview der Woche ist Bernhard Mattes, Vorsitzender der Geschäftsführung von Ford Deutschland.
-Herr Mattes, nicht nur das Auto wird sich in Zukunft verändern, sondern auch wie es gebaut wird, Stichwort """""""""""""""""""""""""""""""" Industrie 4.0"""""""""""""""""""""""""""""""" , also die Vernetzung der gesamten Wertschöpfungskette.
-Vor rund 100 Jahren hat Ford eines der ersten permanenten Fließbänder in der Produktion eingeführt.
-Betrachten Sie sich auch in Sachen Industrie 4.0 als Vorreiter, sozusagen aus der historischen Tradition heraus?
-Mattes: Die Weiterentwicklung der Effizienz unserer Produktion ist schon immer eine hohe Priorität bei uns gewesen, sehr effizient Produkte zu fertigen ist auch eine Notwendigkeit insbesondere, wenn sie im Volumensegment sind, da haben die Kosten natürlich einen hohen Stellenwert, beziehungsweise die Kosten möglichst gering zu halten.
-Und wir haben mit Industrie 4.0 schon sehr, sehr früh angefangen und heute haben wir Industrie 4.0 in vielen, vielen Bereichen komplett umgesetzt.
-Das heißt, wir sind nicht nur, was die Fertigung angeht, in der Planung vollkommen virtuell erstmal unterwegs.
-Wir planen die einzelnen Stationen virtuell, wir wissen, welche Gewichte dort verarbeitet werden müssen, wie das alles abläuft, das wird alles virtuell dargestellt, um dann die Arbeitsabläufe so optimal wie möglich zu gestalten.
-Die Vernetzung mit den manuell tätigen Mitarbeiterinnen und Mitarbeitern und Computern und Robotern haben wir ebenfalls schon hier in die Tat umgesetzt.
-Und letztlich kommunizieren auch schon Teile bei der Produktion miteinander.
-Wenn Sie sich unsere Motorenfertigung anschauen, da wissen die einzelnen Bauteile, welches von seiner Ausprägung, von seiner Größe in ganz genauer Messgenauigkeit, in hoher Messgenauigkeit zum anderen am besten passt.
-Und so werden die Motoren dann auch zusammengebaut.
-"""""""""""""""""""""""""""""""" Es kommen natürlich andere Voraussetzungen auf die Mitarbeiter zu"""""""""""""""""""""""""""""""" Hahne: Und was heißt das für die Mitarbeiter von heute?
-Mattes: Nun, es kommen natürlich andere Voraussetzungen auf die Mitarbeiter zu.
-Neben der manuellen Tätigkeit ist die Bedienung von Computern, von Maschinen, von Robotern heute eine Aufgabe, die fast gang und gäbe geworden ist.
-Das ist auf der einen Seite etwas Neues, auf der anderen Seite natürlich auch für die Mitarbeiterinnen und Mitarbeiter spannend, etwas Neues hinzulernen zu können.
-Und letztlich macht es aber auch die Arbeit leichter, weil wir, wenn Sie sich unsere Produktion anschauen, viele, viele früher beschwerliche Arbeitsgänge heute über Computerisierung, über Roboter und Ähnliches ganz anders gestaltet haben, und die körperliche Beanspruchung der Mitarbeiterinnen und Mitarbeiter ist deutlich geringer.
-Hahne: Im Business Barometer der deutsch-amerikanischen Handelskammer kam heraus, dass etwa ein Viertel der amerikanischen Unternehmen in Deutschland mit mehr Arbeitsplätzen rechnen durch Industrie 4.0, etwa genauso viel allerdings auch mit weniger.
-Was glauben Sie denn?
-Mattes: Also, wir sehen es ja bei uns: Trotz der Umsetzung von Industrie 4.0 an unseren Standorten ist die Anzahl der Belegschaft nicht zurückgegangen.
-Es hat sich aber ein Wandel in den Arbeitsplätzen ergeben, wie ich vorhin schon ausführte.
-Die sind anspruchsvoller geworden, da sind neue Themen hinzugekommen, die auch neu gelernt werden mussten.
-Wir haben ein hohes Maß an Training aufgewandt in den letzten Jahren, wenn es zu neuen Produkten und neuen Produktionsformen kam.
-Also, wir sehen keinen Schwund an Arbeitsplätzen, aber eine andere Qualität an Arbeitsplätzen.
-Hahne: Wenn wir von den Fachkräften der Zukunft sprechen - als im letzten Jahr viele Flüchtlinge nach Deutschland gekommen sind, war die Wirtschaft zunächst relativ euphorisch.
-Die Hoffnung, die mitschwang, war: die Zuwanderung könnte unser demografisches Problem lösen.
-Mittlerweise ist klar, automatisch wird das nicht passieren.
-Ford hat ein Praktikantenprogramm für Flüchtlinge – welche Erfahrungen haben Sie gesammelt?
-Mattes: Also, wir hatten schon die ersten Flüchtlinge in diesem Programm.
-Wir haben positive Erfahrungen gesammelt in mehrerlei Hinsicht.
-Erstens einmal, das waren hochmotivierte oder sind hochmotivierte Menschen, die sich in ein solches Programm begeben, weil sie wissen, was auf sie zukommt.
-Sie werden lernen müssen, sie werden körperlich arbeiten müssen und die deutsche Sprache erlernen, also dreierlei Voraussetzungen.
-Das ist sehr positiv angelaufen.
-Wir werden jetzt eine nächste Gruppe von 24 Flüchtlingen in dieses Qualifizierungsprogramm bringen, wo sie eben soweit fit gemacht werden, dass sie dann im Arbeitsmarkt in eine reguläre Ausbildung einsteigen können.
-Und das hat sich bewährt und wir sind froh, dass wir eben diese Plätze auch bereitstellen können.
-Denn wichtig ist, dass die Menschen, die es wollen, tatsächlich auch die Voraussetzungen schaffen, um dann im Arbeitsmarkt erfolgreich sein zu können.
-Hahne: Arbeiten die eigentlich nur in der Produktion oder auch in der Verwaltung?
-Mattes: Nein, die sind in der Produktion, und da können wir auch genau sehr schön im Prinzip abbilden, was die Leute können und was die Leute wollen, und das passt hervorragend zusammen.
-"""""""""""""""""""""""""""""""" Protektionismus ist in einer immer vernetzteren Welt genau das Falsche"""""""""""""""""""""""""""""""" Hahne: Sie sind nicht nur als Manager in einem deutsch-amerikanischen Konzern ein USA-Kenner, Sie waren schon als Jugendlicher das erste Mal in den USA bei einer Gastfamilie.
-Aktuell läuft ja dort der Präsidentschaftswahlkampf auf Hochtouren.
-Beide Kandidaten schlagen protektionistische Töne an.
-Sorgt Sie das einerseits als USA-Liebhaber, andererseits aber auch als Manager?
-Die USA sind ja immerhin auch der wichtigste Exportmarkt für Deutschland.
-Mattes: Grundsätzlich, ungeachtet jetzt des Präsidentschaftswahlkampfs, ist Protektionismus in einer immer vernetzteren Welt genau das Falsche.
-Freier und fairer Handel, offene Grenzen – aber wie ich sagte, fair auch was Währungsgestaltung angeht –, das ist etwas, was wir befürworten, was ich befürworte, was Ford befürwortet und was auch sicherlich für die USA schon immer etwas war.
-Die USA war immer offen, offen in der Entwicklung neuer Ideen und diese dann auch in die Welt hinauszutragen und nicht nur für sich selber zu sorgen.
-Von daher gesehen bin ich überzeugt, dass es das richtige Mittel ist, weiterhin freien und fairen Handel und wenig Protektionismus zu fordern und zu fördern.
-Wir werden sehen, welcher der Kandidaten letztlich Präsidentin oder Präsident wird.
-Und ich bin überzeugt, dass der Grundsatz von freiem und fairen Handel auch den nächsten Präsidenten oder die nächste Präsidentin schnell überzeugen wird.
-Hahne: Haben Sie da bei Clinton oder Trump größere Hoffnung, bei dem ein oder anderen Kandidaten?
-Mattes: Ich sehe zumindest in den Ankündigungen, dass Frau Clinton eher für einen offenen Handel ist, sicherlich sehr dezidiert und unterschiedlich, was die derzeit diskutierten Freihandelsabkommen angeht – das transpazifische eher kritisch, das europäisch-amerikanische, glaube ich, eher offen.
-Natürlich weist sie auf einige Punkte hin, wie Arbeitnehmerrecht und Ähnliches, aber das ist klar.
-Das ist in den Verhandlungen jetzt auch noch zu Ende zu verhandeln, aber vom Grundsatz her, glaube ich, ist da eine Offenheit da.
-Starke Wettbewerbsposition für mehr Innovation und sichere Arbeitsplätze Hahne: Hillary Clinton wäre Ihnen also die liebere US-Präsidentin?
-Mattes: Das will ich jetzt damit nicht gesagt haben.
-Ich glaube auch, dass ein anderer Präsident, nämlich Donald Trump als Wirtschafskenner, sehr schnell erkennt, dass Protektionismus keine Dauerlösung ist, sondern letztlich Weltoffenheit, wenn es darum geht, Innovationen, Investitionen und auch Handel zu fördern, das richtige Mittel ist.
-Hahne: Es klang ja schon an, Sie sind auch Befürworter des Freihandelsabkommens TTIP. Mittlerweile ist ja nicht mehr so sicher, ob das bis November abschließend verhandelt wird und ob es danach eine Chance hat, das wird dann eben die Zukunft zeigen.
-Würden Sie im Zweifelsfall – anders als früher – jetzt auch für einen Teilbeschluss von einzelnen Paketen plädieren?
-Mattes: Das hat zwei Aspekte.
-Auf der einen Seite, wenn man sich heute dazu durchringt zu sagen: Okay, wir machen einen Teilabschluss – dann hat man vielleicht einen Teilsieg errungen, indem wir einen Teil von Reglungen tatsächlich dann harmonisieren und offen gestalten, aber das Andere ist dann eben nicht geregelt.
-Und deswegen bin ich nach wie vor dafür, keine Ausschlüsse zu machen und ein so umfassend wie mögliches Abkommen zu gestalten und einen Rahmenentwurf bis zum Jahresende zu setzen, der ja dann erstmal in die parlamentarische Beratung auch geht und sowohl in den USA als auch in den europäischen Ländern zu diskutieren ist.
-Möglichst umfassend ist wichtiger als Zeit.
-Zeit ist aber auch drängend, denn wir sind ja nicht alleine im Welthandel, Europa und Amerika.
-Und je mehr Zeit ins Land geht, desto weniger stärken wir die Wettbewerbsposition von Europa und Amerika im Welthandel und das sollten wir uns immer vor Augen führen: Eine starke Wettbewerbsposition hat zum Beispiel auch zur Folge, dass die in diesen Ländern ansässigen Industrien eine bessere Möglichkeit haben, Arbeitsplätze zu sichern, Innovationen zu fördern und letztlich auch Investitionen zu treiben, die weitere Arbeitsplätze schaffen können.
-"""""""""""""""""""""""""""""""" Am Anfang hätte man transparenter informieren sollen"""""""""""""""""""""""""""""""" Hahne: Stichwort """""""""""""""""""""""""""""""" parlamentarische Beratung"""""""""""""""""""""""""""""""" , wie zufrieden stellt Sie denn – als Bürger Bernhard Mattes und nicht als Ford-Chef Bernhard Mattes – der Ablauf der Verhandlungen, der ja insbesondere am Anfang doch recht intransparent war?
-Mattes: Ja, ich habe das persönlich auch genauso gesehen, wie Sie es eben fragen.
-Am Anfang hätte man transparenter informieren sollen.
-Das Mandat, das der EU-Kommission gegeben wurde, ist sehr klar, es wurde von allen 27 Mitgliedsstaaten ratifiziert.
-Das hätte man ohne Weiteres zu Beginn der Verhandlungen und nicht erst zwei Jahre später veröffentlichen können.
-Denn darin können heute alle Bürger lesen – jetzt ist es ja schon lange transparent und im Internet verfügbar –, was sind denn eigentlich die Grundlinien und Richtwerte und Felder der Verhandlungen.
-Da ist alles sehr transparent beschrieben.
-Da ist auch klar beschrieben, in welche Richtung zu verhandeln ist, was das Mandat ist und was es nicht ist.
-Das hätte man früher machen sollen.
-Hahne: Und jetzt nochmal Frage an den Manager: Besonders kritisch diskutiert werden ja die Schiedsgerichte nach wie vor – die politischen Systeme in den USA und Europa bieten Unternehmen ja ziemlich viel Rechtssicherheit.
-Halten Sie Schiedsgerichte trotzdem für ein geeignetes Instrument zum Investorenschutz?
-Mattes: Auf jeden Fall.
-Und ich halte das auch innerhalb von TTIP für das richtige Instrument.
-Weil TTIP kann auch eine Art Blaupause für weitere Freihandelsabkommen sein oder auch ein Abkommen eines Wirtschaftsraumes, der sich weiter öffnen kann, auch weitere Mitglieder noch aufnehmen kann.
-Und um genau diese Möglichkeit aufrecht zu erhalten, sollte man über den Investorenschutz und die Schiedsgerichte auch hier eine Klausel finden.
-Wir haben es ja auch in CETA, in dem Abkommen zwischen der EU und Kanada drin – auch zwei Systeme, die absolut von der Rechtssicherheit in Ordnung sind.
-Es gibt natürlich schon ein Gefälle auch innerhalb der EU, das darf man nicht verkennen.
-Trotzdem, die Bundesrepublik Deutschland hat in 130 Fällen in Freihandelsabkommen Schiedsgerichtsklauseln und Investorenschutzabkommen verankert.
-Um einfach eines sicherzustellen, dass Firmen sowohl im Inland als auch im Ausland, wenn es um willkürliche Veränderungen und Diskriminierung geht, hier vorgehen können.
-Es gilt auch für kleinere Unternehmen, kleinere und mittlere, die mittlerweile ja auch global unterwegs sind, die im Zweifelsfall gar nicht die Möglichkeit haben, weil sie gar nicht die Rechtsabteilungen in ihren Unternehmen haben, ihre Rechte einzufordern.
-Es geht nicht darum, dass man gegen bestehendes Gesetz und Recht klagen kann, dafür ist die normale Gerichtsbarkeit zuständig.
-Das ist auch ein wichtiger Unterschied, der zu machen ist.
-Hahne: Herr Mattes, vielen Dank für das Gespräch.
-Mattes: Bitteschön.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ich glaube, dass die Rolle des Staates wieder wichtiger geworden ist und die Zeit, in der uns Konservative und Liberale eingeredet haben, man müsse eigentlich den Staat immer kleiner werden lassen, dass die vorbei sind.
-Geers: Sind das die Themen, mit denen die SPD auch in den Wahlkampf ziehen will?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" In den schwierigsten Stadtteilen müssen die besten Schulen stehen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Das sind erst mal die Themen, von denen ich den Eindruck habe, dass sie viele Menschen von allen Parteien erwarten und dass wir darüber reden müssen.
-Ich bin übrigens auch nicht dafür, dass wir einen überbordenden Staat bekommen.
-Aber ich bin schon dafür, dass wir wieder zeigen, dass wir die ganz normalen Dinge leisten können, dass wir Schulen sanieren.
-Ich bin eingeschult in eine neue Grundschule, dann bin ich in eine neue Mittelschule gekommen, dann in ein neues Gymnasium, ich konnte richtig anfassen, dass Bildung was wert ist, die sanitären Anlagen in den Schulen waren besser als bei uns zu Hause.
-Und heute haben wir einen riesigen Sanierungsstau in unseren Bildungseinrichtungen.
-Ich finde, dass in den schwierigsten Stadtteilen die besten Schulen stehen müssen, das müssen Leuchttürme sein.
-Nicht die Banktürme sind die Kathedralen unseres Landes, sondern die Schulgebäude.
-Und man kann nicht immer den Eltern sagen: Nehmt einen Eimer Farbe in die Hand und macht es selber – damit ist es nicht getan, wir brauchen auch Lehrer, Sozialarbeiter.
-Da zu investieren, das ist ja nichts, wo ein Mensch, der das von der Politik fordert, jetzt was irgendwie Unbotmäßiges oder nicht Bezahlbares fordern würde, das sind ganz normale Dinge.
-Dass man, wenn man arbeitet, anständige Geld verdient, dass wenn man Rentner ist, sicher ist, dass die Mieten nicht explodieren, dass es bezahlbare Wohnungen gibt, das sind die Themen, die Menschen von der Politik erwarten.
-Und die Zeit, in der sie immer vertröstet wurden, dass das nun mal so ist in der Globalisierung, dass man das nicht alles machen kann und wir kein Geld haben, da sehen die Menschen jeden Tag, dass wir für alles mögliche Geld haben und erwarten – zu Recht –, dass wir diese ganz normalen Bedürfnisse auch erfüllen in unserem Land.
-Geers: Ist das jetzt gerade der Einblick gewesen in das, womit Ihre Partei im nächsten Jahr punkten will in der Bundestagswahl?
-Ich frage das auch vor dem Hintergrund, dass Ihr Hauptgegner, sprich die CDU/CSU, einen eher personalisierten, auf Angela Merkel zugeschnittenen Wahlkampf führen dürfte – den Sie dann mit SPD mit Sachthemen kontern werden?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Wir müssen die Ausgaben für Forschung und Entwicklung erhöhen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Also jedenfalls ist das, glaube ich, was Vernünftiges, dass wir sagen, was wir machen wollen im Land.
-Ich will vielleicht noch etwas hinzufügen, was genauso wichtig ist.
-Wenn man das alles schaffen will, auch wieder mehr Sicherheit – soziale wie innere – zu schaffen, muss man ja sagen: Wo kommt das Geld eigentlich her dafür?
-Und ich glaube, was das Wichtigste ist, dass wir alles dafür tun, dass unser Land wirtschaftlich erfolgreich bleibt.
-Meine Sorge – und das muss auch ein Thema im Wahlkampf sein – ist, dass wir zu viel, sagen wir mal, uns ausruhen auf den Anstrengungen der Vergangenheit und dass wir ein bisschen zu wenig dafür tun, was morgen kommt.
-Ich glaube, wir müssen unsere Ausgaben für Forschung und Entwicklung erhöhen.
-Wir werden dafür sorgen müssen, dass junge Unternehmen mehr Chancen haben.
-Wir müssen dafür sorgen, dass die berufliche Bildung wieder an Stellenwert gewinnt – wir haben einen Fachkräftemangel bei uns.
-In der Energiepolitik haben wir, Gott sei Dank, viel geschafft, sie ist endlich wieder planbar und berechenbar geworden.
-Aber es wird auch darum gehen müssen, Investitionen in die Digitalisierung zu schaffen, die Infrastruktur zu verbessern.
-Nur wenn wir gute wirtschaftliche Rahmenbedingungen haben, dann bleibt es so wie heute, dass wir eine hohe Beschäftigtenzahl haben, dass wir endlich wieder steigende Löhne haben, auch besser Renten haben.
-Wir haben jetzt eine Rentenerhöhung gehabt, die hatten wir in den letzten 20 Jahren nicht so hoch, mit knapp sechs Prozent.
-Das, glaube ich, gehört auch dazu, dass wir in den nächsten zwölf Monaten auch darüber diskutieren müssen in Deutschland: Was ist notwendig, damit das Land erfolgreich bleibt.
-Das sind die beiden Dinge, mehr Sicherheit zu schaffen, aber auch den Erfolg der deutschen Wirtschaft, die Schaffung von Arbeitsplätzen zum Thema zu machen.
-Ich fände es jedenfalls gut, wenn es in einem Bundestagswahlkampf um die Zukunft unseres Landes ginge und nicht nur um die Frage, wer irgendwie die besten Personen aufstellt.
-Geers: Die SPD muss natürlich auch die Frage beantworten: Wie wird das bezahlt?
-Also, wenn ich jetzt überlege oder wenn ich jetzt zusammenzähle: Mehr innere Sicherheit, mehr äußere Sicherheit, Bekämpfung des Terrorismus, Bekämpfung vielleicht auch von Fluchtursachen in Ländern wie Syrien oder in Afrika, wenn ich an weitere Stichworte, die auch immer in der Debatte fallen, wie mehr Geld für die Bundeswehr oder – wie Sie es gerade gesagt haben, Herr Gabriel – mehr Geld für soziale Sicherheit, für den sozialen Zusammenhalt im Land, mehr Geld für Bildung, vielleicht auch mehr Geld für Wachstum in Europa nach einem möglichen Brexit, da kommt Vieles zusammen.
-Und dann muss natürlich auch die SPD Antwort geben darauf, dass es das alles nicht zum Nulltarif gibt.
-Also, woher kommt das Geld?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Formen legaler Steuervermeidung bekämpfen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Erstens haben wir das große Glück, dass wir in einer Phase leben, wo es uns wirtschaftlich gut geht und wir Überschüsse produzieren.
-Wir wären nicht klug beraten, wenn wir die nicht investieren würden in Bildung und in Infrastruktur - das ist die Zukunft unseres Landes.
-Zweitens wird es auch darum gehen - Sie haben das Stichwort völlig zurecht genannt -, was machen wir eigentlich in Europa.
-In Europa ist es heute so, dass jeder Bäckermeister in Deutschland höhere Steuersätze zahlt als große Konzerne wie Amazon, Google und manche anderen, Starbucks, weil wir in Europa Steueroasen haben und dann gigantische Gewinne zum Beispiel in Deutschland gemacht werden, aber nur ein Prozent Steuern gezahlt werden.
-Unser Land verliert nach Berechnungen der Europäischen Kommission in jedem Jahr 150 Milliarden Euro durch diese Form legaler Steuervermeidung - das ist die Hälfte des Bundeshaushaltes!
-Ich glaube nun auch nicht, dass wir das alles kriegen werden, aber stellen Sie sich vor, wir würden es schaffen, wenigstens zehn Prozent davon zu bekommen, indem wir in Europa diese Briefkastenfirmen bekämpfen, dass wir eine gemeinsame Grundlage der Besteuerung haben.
-Ich will ja gar nicht gleiche Steuersätze - das ist eine Illusion, das wird man nicht hinkriegen -, aber dass wir uns wenigstens darauf verständigen, was besteuern wir.
-Das muss Europa schaffen.
-Wenn nicht, werden die Menschen immer weniger bereit sein, sagen wir mal, in Europa etwas zu erkennen, was ihren Lebensinteressen entspricht.
-Und es kann nicht sein, dass der Stärkste sich davor drückt, zum Gemeinwohl beizutragen.
-Das ist auch ein großes europäisches Thema.
-Geers: Das heißt aber auch, aus Ihrer Sicht wackelt dann zum Beispiel das Thema Haushaltsausgleich – dann wackelt die schwarze Null nicht unbedingt?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Es ist kein Ziel per se, Schulden zu machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Also, ich weiß nicht genau, warum man Spaß daran haben soll, Schulden zu machen, sondern das Schönste ist natürlich, wenn man keine macht.
-Und deswegen, es ist ja kein Ziel per se, Schulden zu machen.
-Ich glaube, dass die Frage, ob man sich verschuldet oder nicht, mit zwei zentralen Fragen zu tun hat.
-Erstens, sind es Daueraufgaben, für die man sich verschuldet, dann darf man das eigentlich nicht machen.
-Oder sind es Investitionen, die man tätigt, damit die Bedingungen gut werden in der Infrastruktur, in der Digitalisierung, dann darf man das natürlich, wenn man eine zweite Bedingung einhält und gleich klärt, wie man eigentlich das wieder abbezahlt.
-Und der Fehler der Politik der Vergangenheit ist in der Regel gewesen, dass sich gerade um die zweite Frage keiner Gedanken gemacht hat.
-Ich persönlich bin froh darüber, dass wir in einer Situation leben, in der wir das nicht müssen, in der wir ausgeglichene Haushalte haben.
-Und das ist der Grund, warum ich als Wirtschaftsminister sage: Das klappt alles nur, weil wir eine gut laufende Wirtschaft haben.
-Und das bedeutet: Wer das in Zukunft auch haben will, der muss die Bedingungen für erfolgreiche Wirtschaft in Deutschland gut halten.
-Und da gibt es eine Reihe von Dingen, wo wir in den letzten Jahren, glaube ich, nicht genug gemacht haben.
-Geers: Als da wären?
-Gabriel: Zum Beispiel die Entlastung von mittelständischen Unternehmen dort, wo sie junge Unternehmen haben, wo die Unternehmen investieren wollen.
-Wir haben Regeln,die zum Teil 15,20 Jahre alt sind bei der Frage, was können sie an kurzlebigen Wirtschaftsgütern von der Steuer absetzen, welche Vorschriften müssen sie einhalten, wenn sie ein junges Unternehmen gründen.
-Wir haben jetzt, Gott sei Dank, zwei Bürokratieentlastungsgesetze mit insgesamt mit mehr als zwei Milliarden Euro Entlastung gemacht.
-Aber ich sage Ihnen: Da ist noch mehr drin!
-Dann die Frage Fachkräfte, die Digitalisierung.
-Wir werden in Deutschland auf Sicht keine Chance haben, wirtschaftliche Erfolge zu haben, wenn wir nicht wesentlich besser werden bei der digitalen Infrastruktur.
-Wir haben jetzt ein Ziel von 50 Megabit pro Sekunde im Jahr 2018.
-Das ist in Ordnung, aber jeder weiß: Das ist viel zu wenig.
-Eigentlich muss Deutschland, muss sich Europa das Ziel setzen, im Jahr 2025 die beste digitale Infrastruktur der Welt zu haben – ohne das werden wir das nicht schaffen.
-Das sind Dinge, die als Voraussetzung geschaffen werden müssen, damit die Wirtschaft gut läuft.
-Geers: Würden Sie soweit gehen, Herr Gabriel, dass Sie sagen, mit Blick auch auf die aktuell ja eher günstige Lage, was die Finanzierungsmöglichkeiten des Staates betrifft – er zahlt ja so gut wie keine Zinsen derzeit, der Staat, Deutschland –, dass man diese Zeiten nutzen sollte möglicherweise, um auch für solche Projekt, die man ja definieren könnte als sinnvoll, zukunftsgewandt und, und, und, dass man sagt, für solche Projekte machen wir auch Schulden und haben dann eben jetzt die Möglichkeit, jetzt für vergleichsweise preiswertes Geld Zukunftsinvestitionen zu tätigen?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Für die Digitalisierung wäre ich dafür, Schulden zu machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Alle auf der Welt sagen uns das. Alle. Es gibt nur einen, der anderer Meinung ist, das ist der Bundesfinanzminister.
-Weil alle Ökonomen sagen: 'Ihr seid ja verrückt, dass ihr eure Schulen und eure Infrastruktur verkommen lasst in einer Zeit, wo euch die Investitionen zur Sanierung von Infrastruktur und Schulen nichts kostet und in paar Jahren müsst ihr es dann doch machen und wenn ihr Pech habt, sind die Zinsen dann höher.
-' Es spricht viel dafür, für Investitionen in die Infrastruktur im Zweifel auch bereit zu sein, sich zu verschulden.
-Aber ich sage noch mal: Das kann kein Ziel an sich sein.
-Zurzeit haben wir mit Hilfe auch von Wolfgang Schäuble und der Bundesregierung insgesamt ja zum Beispiel die kommunale Investitionsmöglichkeit deutlich erhöht und mussten dafür überhaupt keine Schulden machen.
-Zweitens, wenn man das macht – zum Beispiel für die Digitalisierung wäre ich dafür, es zu tun –, dann muss man auch eine Vorstellung darüber haben, wie man das zurückzahlt.
-Ein Thema dabei ist – muss man auch offen sagen –, dass ich zum Beispiel glaube, dass es nicht in Ordnung ist, dass wir die Einkommen durch Arbeit stärker besteuern als die Einkommen die man hat, wenn man Aktien besitzt.
-Es kann ja nicht sein, dass einer, der arbeiten geht, höhere Steuern zahlt auf den gleichen Betrag, als jemand, der auf dem Sofa liegt und das über die Aktien bekommt.
-Das haben wir mal eingeführt, weil wir gehofft haben, dass die Steuerflucht nachlässt.
-Heute haben wir Datenaustausch, es gibt kein Bankgeheimnis mehr, wir können die Steuerhinterziehung anders bekämpfen.
-Geers: Also, Abgeltungssteuer abschaffen?
-Gabriel: Die Abgeltungssteuer ist der Fachbegriff dafür.
-Und das Geld, das wir dort bekommen, sollten wir ausschließlich in den Bildungsbereich stecken.
-Ein großes Schulsanierungsprogramm, Sanierung der Sportstätten, Einstellung von Sozialpädagogen in den Ganztagsschulen.
-Das wäre ein großes Programm, was auch mal zeigen würde: Bildung ist uns was wert!
-Geers: Sagt Sigmar Gabriel, der Vizekanzler, der SPD-Chef und der mögliche SPD-Kanzlerkandidat, der dabei bleibt, dass diese Entscheidung erst Anfang nächsten Jahres getroffen wird?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Erst mal sagen, was man will und dann eine Person bestimmen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gabriel: Ich habe schon darauf gewartet, dass die Frage kommt.
-Geers: Ich stelle sie am Schluss.
-Gabriel: Ja, ist ja auch in Ordnung.
-Ich meine, ich will es einfach nur erklären.
-Wenn wir jetzt anfangen, Personal bei uns zu debattieren, können Sie als Journalisten überhaupt nicht anders, als nur darüber zu reden.
-In dem Interview hier war es deshalb gut, weil wir fast nur über Sachfragen geredet haben, sonst hätten wir ausschließlich über Personen geredet – ist meine Vermutung.
-Und ich glaube, dass es klug ist, erst mal zu sagen, was man will und dann am Ende auch eine Person – natürlich brauchen wir die – zu bestimmen und es nicht umgekehrt zu machen.
-Und dann bin ich ein bisschen lästerlich und sage: Solange die Kanzlerin noch nicht einmal gesagt hat, ob sie noch mal kandidiert, müssen wir noch keinen Kandidaten nennen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Die Aufgewühltheit vieler Menschen, die Unzufriedenheit, 
 Ich glaube, wir müssen schon zeigen, dass das Pendel jetzt in die andere Richtung ausschlägt: 
@@ -277,211 +50,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Beweise aus diesem syrisch-irakischen Kriegsgebiet zu gewinnen.
-Wir haben auch sehr viele Beweismittel hier in Deutschland.
-Allein mit dem Flüchtlingsstrom sind auch sehr viele geschädigte, geschundene Personen, vertriebene Personen, die Opfer des sogenannten Islamischen Staates geworden sind, hierher nach Deutschland gekommen.
-Auch insoweit stehen uns sehr viele Beweismittel als Zeugen zur Verfügung.
-Geuther: Und nur, um das noch mal klarzustellen, ich hatte die Frage jetzt eingeleitet über die Flüchtlinge, aber von den mehr als 130 Verfahren, die Sie führen, ist das natürlich nur der allergeringste Teil.
-Wir haben ja bisher im Zusammenhang mit Syrien vor allem über die verschiedenen islamistischen Organisationen gesprochen.
-Der syrische Menschenrechtsanwalt Ibrahim Alkasem hat vor Kurzem in der Online-Ausgabe der """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Zeit"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" an Sie appelliert, systematisch und strukturiert auch insbesondere Folter durch die Assad-Seite in den Blick zu nehmen.
-Frank: Wir haben nicht nur terroristische Organisationen im Blick.
-Die Bundesanwaltschaft ist seit dem Inkrafttreten des Rom-Statuts ja mit der Umsetzung und mit der Verfolgung von Straftaten nach dem Völkerstrafgesetzbuch – das zeitgleich in Kraft getreten ist – beauftragt.
-Wir führen – was den syrisch-irakischen Bürgerkrieg anbelangt, mehrere Strukturverfahren, um zu beobachten und herauszufinden und zu ermitteln und Beweise zu sichern: Wer könnte Kriegsverbrechen begehen, Verbrechen gegen die Menschlichkeit?
-Wir haben da sowohl den sogenannten Islamischen Staat im Blick, wir haben da aber auch das Regime im Blick.
-Und insoweit ist es für uns auch wichtig, Beweise, Beweismittel – das sind in der Regel Zeugen, die als Flüchtlinge hierher nach Deutschland gekommen sind –, diese Beweismittel zu sichten, auch in Kooperation mit anderen ausländischen Staaten.
-Denn Flüchtlinge sind ja nicht nur nach Deutschland gekommen.
-Insoweit stehen wir in einem engen Austausch mit anderen Staatsanwaltschaften anderer europäischer Länder, in denen auch entsprechende War Crime Units gebildet wurden, um hier gemeinsam Beweise zu sichern, die wir vielleicht einmal nutzbar machen können, wenn Teilnehmer solcher Kriegsverbrecherhandlungen hierher nach Deutschland kommen.
-Geuther: Sie hören das Interview der Woche im Deutschlandfunk mit Generalbundesanwalt Peter Frank.
-Herr Frank, noch vor einigen Wochen hätten wir dieses Gespräch wahrscheinlich mit dem Schwerpunkt Rechtsextremismus begonnen.
-Sie haben mehrere Verfahren übernommen.
-Im April haben Sie fünf Personen festnehmen lassen wegen des Verdachts der Mitgliedschaft in einer rechtsterroristischen Vereinigung.
-Dieser """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gruppe Freital"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" rechnen Sie auch noch weitere Personen hinzu.
-Hätten Sie sich ohne die Erfahrung mit dem NSU vorstellen können, dass es Terrorismus von rechts in Deutschland geben könnte?
-Frank: Durch die Erkenntnisse aus dem NSU-Komplex hat sich der Blickwinkel auf den Themenkomplex Rechtsextremismus sicherlich noch etwas stärker verstärkt.
-Die Bundesanwaltschaft hat in dieser Folge ein eigenes Referat """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Deutscher Terrorismus rechts"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" gebildet.
-Wir haben in Zusammenarbeit auch mit den Länderbehörden in der Zwischenzeit eine Strategie entwickelt, wie wir das Thema Rechtsterrorismus, Rechtsextremismus auch aus Sicht der Strafverfolgungsbehörden stärker durchleuchten und beleuchten wollen.
-Denn eines muss klar sein: Eine terroristische Organisation wie der NSU, der doch über Jahre hinweg vielleicht unbekannt und unerkannt in Deutschland Morde begangen hat, das darf es nicht mehr geben.
-Und insoweit sind wir in einem engen Austausch und in einer engen Vernetzung, nicht nur mit den Staatsanwaltschaften der Länder, sondern auch mit den Polizeibehörden des Bundes und der Länder, mit den Verfassungsschutzbehörden des Bundes und der Länder.
-Das ist eine gesamtgesellschaftliche Aufgabe.
-Dazu gehört auch, dass der Generalbundesanwalt das eine oder andere Verfahren von den Ländern – das auch dort stärker ermittelt und ausgeleuchtet wird – immer wieder übernimmt.
-Und eine Folge war die Übernahme dieses Verfahrens Freital.
-Geuther: Und gerade da hatte die Aufdeckung der NSU-Taten ja auch tatsächlich Konsequenzen für Ihre Behörde bei der Frage der Übernahme und der Zuständigkeit.
-Dafür muss es ja immer einen besonderen Grund geben, sonst sind die Landesbehörden zuständig.
-Und in der Vergangenheit gab es da auch schon Streit.
-Jetzt müssen die Landesbehörden Sie vor allem früher informieren, wenn es Anhaltspunkte gibt zum Beispiel, ob ein Fall besondere Bedeutung hat.
-Klappt das denn jetzt?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Recht muss immer durchgesetzt werden"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Frank: Wir stehen in einem sehr engen Austausch.
-Wir haben in den letzten anderthalb Jahren diverse Regionalkonferenzen mit den Staatsanwaltschaften, Polizeibehörden, Verfassungsschutzbehörden der Länder, teilweise unter Beteiligung auch von Behörden aus dem Ausland durchgeführt.
-Denn eines muss man sehen: Auch der Rechtsextremismus ist nicht nur auf Deutschland beschränkt.
-Auch hier gibt es immer wieder Kontakte in das Ausland.
-Sei es allein, was die Beschaffung bestimmter pyrotechnischer Gegenstände anbelangt.
-Sei es als Rückzugsgebiete oder Vernetzung mit anderen ausländischen rechtsterroristischen oder rechtsextremistischen Strukturen.
-Wir haben ein Ansprechpartner-Netzwerk entwickelt.
-Wir versuchen auch, dieses noch weiter zu entwickeln, indem wir die Länderstaatsanwaltschaften noch enger an uns heranbinden.
-Und insoweit berichten uns die Länder sehr frühzeitig.
-Wir berichten den Ländern aufgrund unserer Erkenntnisse.
-Und ich glaube, das ist auch das Entscheidende.
-Geuther: Es wurde einzelnen Ländern – gerade auch im Osten der Republik – vorgeworfen, eine Tat später als rechtsextremistisch einzuordnen als andere – vorsichtig gesagt.
-Stimmt das?
-Und wenn ja, stimmt das immer noch?
-Frank: Um hier eine Sensibilisierung auch bei jedem zu erreichen, haben wir, hat die Bundesanwaltschaft, in Zusammenarbeit aber auch mit den Generalstaatsanwaltschaften der Länder verschiedene Instrumentarien entwickelt.
-Eines ist zum Beispiel – auch, wenn das vielleicht banal klingen mag – die Entwicklung eines Formblattes, wie man frühzeitig rechtsextremistische Straftaten erkennen kann.
-Denn vielfach ist ein erster Kontakt mit rechtsextremistischen Straftaten nicht immer dann gegeben, wenn Volksverhetzungen begangen wurden, der Hitler-Gruß gezeigt wird, wenn Hakenkreuze an die Wand gemalt werden.
-Häufig sind es Straftaten der Allgemeinkriminalität.
-Es sind Körperverletzungshandlungen.
-Und hier muss jeder Staatsanwalt frühzeitig wissen – nicht nur der Staatsanwalt, der sich in einer Spezialabteilung befindet –, muss sich jeder Staatsanwalt frühzeitig bewusst werden: Gibt es hier Erkenntnisse, die darauf hindeuten, dass es sich um einen rechtsextremistischen Hintergrund handelt?
-Und insoweit haben wir versucht, jeden Staatsanwalt und im Übrigen auch versucht, jeden Vollzugsbeamten – denn man muss auch im Strafvollzug erkennen: Jemand, der wegen eines Diebstahls, eines Ladendiebstahls sitzt, auch der kann einen rechtsextremistischen Hintergrund haben – frühzeitig diese Strukturen zu erkennen, um sie dann den zuständigen Behörden zu melden, damit sich daraus nichts verfestigt.
-Geuther: Es gab im vergangenen Jahr fast 1.500 politisch rechts motivierte Gewalttaten und darunter eine bisher nie gehabte Zahl von Angriffen auf Flüchtlingsunterkünfte.
-Wie gehen Sie als Generalbundesanwalt damit um?
-Frank: Für die Beobachtung von rechtsextremistischen Straftaten gibt es im Bundesamt für Verfassungsschutz das gemeinsame Extremismus- und Terrorismusabwehrzentrum rechts, in dem auch wir – die Bundesanwaltschaft – vertreten sind.
-In diesem Zentrum, das eine Plattform darstellt, in dem Polizeibehörden, Dienste, Nachrichtendienste, aber auch die Staatsanwaltschaft vertreten ist, werden solche Vorfälle gemeinsam bewertet.
-Wir, die Bundesanwaltschaft, schauen uns diese schwerwiegenden Straftaten, wenn sie ein bestimmtes Ausmaß erreicht haben, immer wieder an, um dort auch herauszufinden, ob sich Strukturen bilden.
-Das ist eine der Konsequenzen auch der Ergebnisse aus der Aufarbeitung NSU, dass wir verschiedene Strukturverfahren angelegt haben, um frühzeitig herauszufinden: Welche Entwicklungen spielen sich in bestimmten Bereichen ab?
-Wir haben – gerade, was die Anschläge auf die Flüchtlingsheime im letzten Jahr anbelangt – Strukturen, Verfahren geführt, um festzustellen: Gibt es Vernetzungen?
-Sind das nur Taten von Einzelpersonen oder von lokalen kleineren Gruppierungen?
-Oder hat sich da eine größere Vernetzungsstruktur gebildet?
-Findet da vielleicht eine Steuerung aus einem etwas größeren Ganzen statt?
-Wir haben auch im Blick, zusammen mit den Polizei- und den Verfassungsschutzbehörden: rechtsextremistische Musikgruppen.
-Wir haben im Blick besonders: rechtsextremistische Gefährder.
-Wir stehen insoweit in einem engen Kontakt und Austausch mit dem Bundeskriminalamt.
-Wir kriegen in regelmäßigen Abständen alle Gefährder aus dem rechtsextremistischen Bereich gemeldet, die wir dann wiederum mit unseren Erkenntnissen versuchen abzuklären.
-Nur, wenn man versucht, das Phänomen Bereich Rechtsextremismus ganzheitlich zu betrachten und unter allen möglichen Aspekten und Blickwinkeln auch zu durchleuchten, dann lässt sich frühzeitig verhindern, dass sich wieder eine neue Struktur NSU bildet.
-Das ist für uns sehr wichtig.
-Geuther: Jetzt haben wir über Rechtsextremismus gesprochen, vorher über den Islamismus, über eine Amok-Tat.
-Gleichzeitig waren laut Verfassungsschutzbericht auch Linksextremisten im vergangenen Jahr deutlich gewalttätiger als zuvor.
-Und man könnte auch weitergehen.
-Die Verrohung steigt offenbar insgesamt.
-Nicht nur in der Sprache im Internet, auch im öffentlichen Dienst, im Arbeitsamt oder in der Ausländerbehörde werden Mitarbeiter öfter angegriffen.
-Was kann Recht da überhaupt leisten?
-Frank: Es ist seit längerer Zeit zu erkennen, dass die Gewaltbereitschaft in Deutschland zugenommen hat.
-Und so, wie Sie es beschrieben haben, es beginnt zunächst einmal mit einer Verrohung der Sprache.
-Und es führt dann zu einer Verrohung auch in der körperlichen Auseinandersetzung.
-Seit Jahren steigt der Anteil von Gewaltstraftaten.
-Und auch, wenn man sich die Entwicklung innerhalb der Gewaltstraftaten anschaut, so findet man immer wieder einen Anstieg auch der Vehemenz von Gewalt.
-Recht – und das ist das Entscheidende und Wichtige von Recht – Recht muss immer durchgesetzt werden.
-Recht muss insoweit standhaft bleiben, denn sonst verliert das Recht seine Achtung.
-Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
-Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
-Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Frank: Ja.
 Zunächst möchte ich vielleicht eines vorweg sagen.
 Flüchtling ist oder einen anderen Aufenthaltstitel hat.
 Wir gehen diesen Hinweisen im Einzelnen nach.
 Da gibt es eine Reihe von Hinweisen, die sich als nichtzutreffend herausgestellt haben.
 Aber immer dann, wenn sich der Verdacht ergibt, ein begründeter Verdacht ergibt,  in einem doch fernab  gelegenen Kriegsgebiet – in dem ja jegliche staatliche Kontrolle, jede jegliche staatliche Struktur zusammengebrochen ist – auch Beweise zu erheben.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>In der Sache – das haben Sie immer deutlich gemacht – stehen Sie hinter ihm, Sie halten diese Fusion für richtig.
-Sind Sie sicher, dass Gabriel auch im schwierigen, heiklen Verfahren, um das es jetzt geht, alles richtiggemacht hat?
-Scholz: Ich kenne die Akten nicht, aber ich bin sehr überzeugt davon, dass das alles richtig gemacht worden ist, was dort in dem Wirtschaftsministerium vorbereitet worden ist und was an Diskussionen stattgefunden hat.
-Immerhin ist es ja so, dass hier ganz bewusst vorgesehen ist, dass es ein geordnetes Verfahren gibt und dann noch eine politische Möglichkeit, eine Fusion zu erlauben aus politischen Erwägungen heraus, zum Beispiel, weil man Arbeitsplätze sichern möchte.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Hier geht es um Männer und Frauen, die sich Sorgen machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Ist das für die SPD auch eine Chance, mal wieder den Schulterschluss mit den Gewerkschaften im Kampf um Arbeitsplätze zu demonstrieren?
-Scholz: Man sollte solche Entscheidungen nicht unter solchen politischen Kriterien fällen – also, was nützt meiner Partei –, sondern hier geht es um viele Männer und Frauen, die in den Unternehmen arbeiten und die sich Sorgen um ihre Zukunft machen.
-Detjen: Ich habe das gefragt, weil sich der Bundeswirtschaftsminister mit dieser Entscheidung ja gegen die Empfehlung beziehungsweise Entscheidung derer hinweggesetzt hat, die für den freien Wettbewerb zuständig sind – Bundeskartellamt, Monopolkommission –, die eine andere Entscheidung empfohlen oder nahegelegt haben.
-Scholz: Er ist nicht der Erste, der das tut.
-Minister, die dieses Amt vor ihm hatten, aller Parteien, haben schon solche Genehmigungen erteilt.
-Und es wird auch nicht die letzte sein.
-Detjen: Herr Bürgermeister, wir stehen gut ein Jahr vor der Bundestagswahl.
-Das könnte die Zeit sein, eine vorläufige Bilanz der Großen Koalition zu ziehen, mit der sich Ihre Partei, die SPD, am Anfang ja schwergetan hat.
-Wie ist Ihre Bilanz ein Jahr vor der Bundestagswahl?
-Scholz: Wir haben viele Erfolge durchsetzen können.
-Der wichtigste ist sicherlich die Einführung eines allgemeinen, gleichen, flächendeckenden Mindestlohns in Deutschland.
-Deutschland ist Nachzügler.
-Das gibt es in vielen, vielen vergleichbaren Ländern – jetzt haben wir das auch.
-Und es gibt Verbesserungen etwa im Bereich der Sicherheit von Arbeitsplätzen und von Arbeitnehmerrechten, bei der Leiharbeit, bei Werkverträgen sind wir an der Sache dran.
-Das ist alles wichtig und eine gute Leistungsbilanz.
-Detjen: Das sah ja schon am Anfang dieser Großen Koalition so aus.
-In den ersten Monaten hat die SPD ein Projekt nach dem anderen durchgekriegt.
-Es wirkte so – so haben auch wir in den Medien das beschrieben –, als diktiert die SPD die Agenda dieser Großen Koalition.
-Das flachte dann etwas ab und vor allen Dingen hat es sich in den Umfragewerten nie richtig niedergeschlagen.
-Woran liegt das?
-Scholz: Erstmal ist es wichtig, dass man gute Arbeit leistet und es ist nicht schlecht, dass alle das immerhin attestieren.
-Das ist ja eine gute Empfehlung, wenn es zu Wahlen geht.
-Und im Übrigen geht es bei Wahlen darum, dass wir die Bürgerinnen und Bürger davon überzeugen, dass man uns auch das Mandat, die Regierung zuführen, anvertrauen kann.
-Dann gibt das auch mehr Stimmen und mehr Prozentpunkte als in den gegenwärtigen Umfragen.
-Detjen: Ob man eine Regierung führen will, das war ja auch in Ihrer Partei gar nicht so unumstritten oder so gar nicht fraglos.
-Vor einem Jahr hat sozusagen Ihr Nachbar als Regierungschef, Torsten Albig, der Ministerpräsident von Schleswig-Holstein, noch in Frage gestellt, ob die SPD 2017 überhaupt einen eigenen Kanzlerkandidaten aufstellen sollte.
-Das war vor der Flüchtlingskrise.
-Wie sieht das heute aus?
-Scholz: Wir sind uns alle einig: Wir werden einen Kanzlerkandidaten aufstellen.
-Wir wollen den Kanzler dieser Republik stellen.
-Und Anfang des nächsten Jahres wird der Parteivorsitzende dazu einen Vorschlag machen.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Ein Parteivorsitzender ist immer ein guter Kanzlerkandidat"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Und Sie, das haben Sie immer wieder erklärt, sind dafür, dass Sigmar Gabriel das sein soll?
-Scholz: Ein Parteivorsitzender ist immer ein guter Kanzlerkandidat, sonst wäre er übrigens auch ein schlechter Parteivorsitzender.
-Detjen: Und Sie gehören selbst zu den Mehreren, auf die Sigmar Gabriel auch immer wieder gezeigt hat, die in der SPD noch mögliche Kanzlerkanditen wären.
-Scholz: Das ist ja nichts Schlechtes, dass man das allgemein mehreren Männern und Frauen in der Führung der deutschen Sozialdemokratie zutraut.
-Trotzdem gilt, der Parteivorsitzende wird einen Vorschlag machen.
-Und ich wiederhole es nochmal: Ein Parteivorsitzender ist immer ein guter Kandidat.
-Detjen: Wo ist die Linkspartei zurzeit für Sie ein Regierungspartner der SPD, ein guter Regierungspartner?
-wo in den Ländern?
-Auf Bundesebene auch?
-Scholz: Die Partei Die Linke vertritt politische Positionen im Hinblick auf die Entwicklung unseres Landes, auf die Entwicklung Europas, auf globale Themen, mit denen man sich gegenwärtig nicht vorstellen kann, wie da eine gemeinsame Regierung funktionieren sollte.
-Deshalb kann man beim Blick auf die Partei Die Linke große Skepsis haben, dass die in der nächsten Zeit noch die Wende schaffen, dass sie regierungsgeeignet in einem deutschen Staat sind.
-Ich halte das nicht für möglich.
-Detjen: Das bezieht sich jetzt auf Koalitionen auf Bundesebene, was Regierung angeht.
-Vor der Bundestagswahl, vor der Bildung einer Bundesregierung steht die Wahl eines Bundespräsidenten, eine sozusagen rot-rot-grüne Koalition in der Bundesversammlung.
-Ist das für Sie erstrebenswert?
-Scholz: Ich wünsche mir, dass jemand Präsident oder Präsidentin wird, von dem die Bürgerinnen und Bürger sagen: Das ist ein guter Präsident, das ist eine gute Präsidentin.
-Da geht es nicht zu allererst um Parteipolitik, sondern darum, dass das Land zusammengehalten wird.
-Und das sollte auch im Vordergrund der Bemühungen stehen.
-Ich fände es auch sehr gut möglich, dass sich Parteien der jetzigen Regierung auf einen gemeinsamen Kandidaten verständigen, den auch die Grünen zum Beispiel und andere gut finden.
-Detjen: Herr Scholz, jetzt beginnt für die Parteien, zunächst mal als Vorbereitung auf die Wahl, die Aufstellung der Kandidatenlisten – das betrifft auch die SPD in Hamburg natürlich.
-Können Sie gewährleisten, dass die SPD in Hamburg keine Kandidatinnen oder Kandidaten aufstellt, die dann danach mit gefälschten Lebensläufen den Bürgern etwas vormachen?
-Scholz: Das glaube ich schon.
-Detjen: Das war in Nordrhein-Westfalen offenbar nicht so einfach.
-Was ist da schiefgelaufen?
-Scholz: Weiß ich nicht.
-Ich kenne mich vor Ort nicht genug aus.
-Ich glaube, dass alle sehr betrübt darüber sind, dass es so ist.
-Und das muss jetzt auch schnell in Ordnung gebracht werden.
-Detjen: Zu den Befunden in dieser Affäre um die SPD-Bundestagsabgeordnete Petra Hinz gehört ja auch das Bild, dass da eine SPD-Abgeordnete war, die eigentlich niemand richtig kannte.
-Der Vorsitzende des SPD-Unterbezirks Essen, der nordrhein-westfälische Justizminister Kutschaty sagt, es habe eigentlich gar keine persönlichen Beziehungen zu dieser Abgeordneten gegeben.
-Schlagen sich da ein paar Genossen jetzt im Nachhinein in die Büsche?
-Oder wirft diese Affäre ein Schlaglicht auf eine für die Politik vielleicht typische Verkümmerung von menschlichen Beziehungen?
-Scholz: Letzteres ganz bestimmt nicht.
-Wie es dazu gekommen ist, dass das niemand bemerkt hat, auch die ja immer sehr kritische Öffentlichkeit und Presse nicht.
-Das kann ich mir auch nicht so richtig erklären.
-Auf alle Fälle, wenn alles zu Ende ist, wird es sicherlich ein gutes Buch über das Thema geben und dann werden wir mehr lernen.
-Detjen: Sie haben vor ein paar Wochen, Herr Scholz, ein Papier geschrieben, das trug die Überschrift: Die Partei der schlechten Laune.
-Das bezog sich nicht auf die SPD, richtig?
-Scholz: Klar, das bezog sich auf die AfD. """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Dafür sorgen, dass es eine gute Zukunft gibt"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Warum ist die für Sie die """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Partei der schlechten Laune"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" ?
-Scholz: Weil es ja keine konkreten Vorstellungen gibt darüber, wie es weitergehen soll mit unserem Land, sondern vor allem der Eindruck erweckt wird, alles läuft schief und es geht in die falsche Richtung.
-Ich glaube, dass es immer wichtig ist, dass man Vorstellungen dafür hat, wie man mit demokratischer Politik unser Land besser machen kann und dass man sich auch auf ganz, ganz, ganz konkrete Fragen beziehen muss.
-Was machen wir mit unseren öffentlichen Haushalten?
-Wie statten wir die Bundeswehr und unsere Polizei gut aus?
-Was machen wir, um die Bildung zu verbessern an den Schulen?
-Wie setzen wir Forschung und Universitäten auf die richtige Spur?
-Also immer ganz konkrete Politik, bei der es darum geht: Wie können wir dafür sorgen, dass es eine gute Zukunft gibt.
-Und über sowas muss man diskutieren.
-Und ich glaube, dass das auch der richtige Umgang ist in der Sache.
-Detjen: Dann werfen wir am Ende des Gesprächs nochmal den Blick auf das konkrete Thema, das uns alle, das das Land im vergangenen Jahr am meisten beschäftigt hat.
-Vor einem Jahr um diese Zeit schwante den meisten, dass mit der Flüchtlingsbewegung eine riesige Aufgabe, eine Generationenaufgabe auf Bund, Länder, Kommunen zukommen.
-Wenn Sie jetzt Hamburg anschauen, was sich in diesem Jahr getan hat, ist das für Sie ein Anlass, gut gelaunt auf die Entwicklung zu schauen oder eher schlecht gelaunt?
-Scholz: Was letztes Jahr stattfand, war eine unglaubliche Herausforderung.
-Und – das, glaube ich, muss man auch ganz offen sagen – in Deutschland war nicht überall klar, wer wann wo ist und wer wohin kommen soll und wer wo aufgenommen wird.
-Mittlerweile sind viele Institutionen, insbesondere auch das Bundesamt für Migration und Flüchtlinge, massiv ausgebaut worden.
-Dieser Ausbauprozess ist noch nicht beendet, das muss nun bald erfolgen.
-Und wir müssen mit den gesetzlichen Änderungen, die wir ergriffen haben, mit all den Maßnahmen, die wir getroffen haben, vorbereitet sein auf solche Entwicklungen.
-Das muss das Ergebnis des letzten Jahres sein.
-Denn wir können ja nicht sicher sein, dass nicht irgendwann mal wieder eine große Zahl von Flüchtlingen kommt.
-Jetzt sieht es ein wenig danach aus, dass es weniger werden und wir uns jetzt auf die Aufgabe konzentrieren können, diejenigen, die länger bleiben werden, zu integrieren.
-Detjen: Nochmal der Blick konkret auf Hamburg.
-Was haben Sie geschafft in diesem Jahr?
-Scholz: Wir haben Tausende von Unterkunftsplätzen geschaffen, was nicht ganz einfach ist in einer Stadt, die sehr bebaut ist und relativ mehr Flüchtlinge aufnimmt als andere, weil bei der Verteilung der Flüchtlinge in Deutschland Bevölkerungszahl und Wirtschaftskraft eine Rolle spielen und nicht die Frage 'Wieviel Platz hat man so?
-'.
-Das haben wir aber gemeistert und haben uns auch über viele Standorte verständigt, haben mit vielen Bürgerinnen und Bürgern gesprochenen, verhandelt, haben unglaublich viel Unterstützung bekommen von denjenigen, die in den Flüchtlingsunterkünften helfen.
-Und wir haben sofort dafür gesorgt, dass mehr Angebote gemacht werden bei Krippen und Kitas, bei den Schulen, haben zusätzliche Lehrerinnen und Lehrer eingestellt, damit es ohne Beeinträchtigung des bisherigen Betriebs zu einer schnellen Integration der jungen Leute kommt.
-Wir haben uns sofort darauf konzentriert, diejenigen, die in dem Alter sind, in dem man zur Berufsschule geht, dort auszubilden, auch mit einer Berufsorientierung zu versehen.
-Und wir haben Angebote entwickelt, die für diejenigen, die erwachsen sind, eine Arbeitsmarktintegration in den Blick nehmen.
-Detjen: Und vieles ist noch zu tun.
-Würden Sie Ihren Bürgerinnen und Bürgern in Hamburg sagen: """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Wir schaffen das"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" ?
-Scholz: Wer realistisch ist, kann immer nur sagen: Wir können das schaffen.
-Aber die Bürgerinnen und Bürger haben einen großen Beitrag dazu geleistet, dass zusammen mit einer sehr engagierten Verwaltung wir ganz schön weit gekommen sind und uns jetzt an die nächsten Aufgaben machen.
-Detjen: Herr Bürgermeister, vielen Dank.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -837,7 +411,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -856,7 +430,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +449,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -894,7 +468,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="224" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +479,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.33203125" customWidth="1"/>
@@ -915,35 +489,11 @@
     <col min="5" max="5" width="24.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/260718.xlsx
+++ b/260718.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711F4FD2-F41C-47AB-AB4F-2A4FDD550C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CDED0A-0EE4-4D1B-8084-30E4F5870510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9260" yWindow="4110" windowWidth="16150" windowHeight="11170" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6240" yWindow="3240" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -29,16 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Die Aufgewühltheit vieler Menschen, die Unzufriedenheit, 
-Ich glaube, wir müssen schon zeigen, dass das Pendel jetzt in die andere Richtung ausschlägt: 
-Die Menschen können diese ganzen Heilsversprechen der Globalisierung der Liberalisierung nicht mehr hören, wenn sie sehen,
-dass ihre eigenen Kinder keinen festen Arbeitsplatz mehr bekommen oder dass man 40 Jahre arbeitet und am Ende eine Rente hat, 
-die kleiner ist, mehr Vertrauen darin existiert, dass sich Leistung lohnt, 
-dass Menschen in sozial schwierigen Lagen Hilfe bekommen, dass der Staat .</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>"aber nicht bei Dingen, die Sie und ich selber in der Hand behalten können, wofür wir überhaupt keine Politik, erst recht keine europäische Politik brauchen.
 Remme: Ich habe den Namen Genscher erwähnt.
@@ -67,6 +58,25 @@
 Die Verhandlungen sind sehr weit zurückliegend.
 Der Zeitplan ist bisher, soweit ich das beurteilen kann, nicht eingehalten.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aufgewühltheit ; aufwühlen 激起</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heilsversprechen</t>
+  </si>
+  <si>
+    <t>existiert, dass sich Leistung lohnt</t>
+  </si>
+  <si>
+    <t>Hand behalten  erst recht</t>
+  </si>
+  <si>
+    <t>Kopfzerbrechen</t>
+  </si>
+  <si>
+    <t>Stabilitätspakt Regeln gebrochen und verwässert</t>
   </si>
 </sst>
 </file>
@@ -403,15 +413,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15DF06C6-D905-4387-99F5-3F4C39DEF066}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -430,7 +465,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -449,7 +484,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -468,7 +503,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="224" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
